--- a/docs/outil-excel/exemple_propositions_IA.xlsx
+++ b/docs/outil-excel/exemple_propositions_IA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="161">
   <si>
     <t>Format</t>
   </si>
@@ -193,6 +193,60 @@
     <t>Mémorandum d'information, p. 9</t>
   </si>
   <si>
+    <t>climat.localisation</t>
+  </si>
+  <si>
+    <t>Province de Ouarzazate</t>
+  </si>
+  <si>
+    <t>Rapport de l'expert technique, p. 30</t>
+  </si>
+  <si>
+    <t>climat.alea.chaleur.niveau</t>
+  </si>
+  <si>
+    <t>Élevé</t>
+  </si>
+  <si>
+    <t>climat.alea.chaleur.adaptation</t>
+  </si>
+  <si>
+    <t>Rapport de l'expert technique, p. 32</t>
+  </si>
+  <si>
+    <t>climat.alea.vents.niveau</t>
+  </si>
+  <si>
+    <t>Moyen</t>
+  </si>
+  <si>
+    <t>climat.emissions</t>
+  </si>
+  <si>
+    <t>Rapport de l'expert technique, p. 34</t>
+  </si>
+  <si>
+    <t>climat.export_macf</t>
+  </si>
+  <si>
+    <t>climat.actif_fossile</t>
+  </si>
+  <si>
+    <t>climat.choc</t>
+  </si>
+  <si>
+    <t>Rapport de l'expert technique, p. 33</t>
+  </si>
+  <si>
+    <t>Faible</t>
+  </si>
+  <si>
+    <t>climat.choc.description</t>
+  </si>
+  <si>
+    <t>Canicule prolongée et vents de sable : production − 5 %, nettoyage + 5 %</t>
+  </si>
+  <si>
     <t>emploi.1.libelle</t>
   </si>
   <si>
@@ -386,9 +440,6 @@
   </si>
   <si>
     <t>Notation interne (à confirmer)</t>
-  </si>
-  <si>
-    <t>Faible</t>
   </si>
   <si>
     <t>duree_contrat</t>
@@ -790,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -1134,67 +1185,67 @@
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28">
-        <v>395</v>
+      <c r="B28" t="s">
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30">
-        <v>22</v>
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="B31">
+        <v>900</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B32">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
         <v>20</v>
@@ -1202,13 +1253,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C33" t="s">
         <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="C33" t="s">
-        <v>71</v>
       </c>
       <c r="D33" t="s">
         <v>20</v>
@@ -1219,38 +1270,38 @@
         <v>72</v>
       </c>
       <c r="B34">
-        <v>300</v>
+        <v>0.06</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" t="s">
         <v>73</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
         <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
         <v>20</v>
@@ -1258,13 +1309,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B37">
-        <v>165</v>
+        <v>395</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>20</v>
@@ -1272,13 +1323,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
         <v>20</v>
@@ -1286,13 +1337,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>79</v>
-      </c>
-      <c r="B39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C39" t="s">
-        <v>81</v>
       </c>
       <c r="D39" t="s">
         <v>20</v>
@@ -1300,13 +1351,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
         <v>20</v>
@@ -1314,13 +1365,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B41">
-        <v>300</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D41" t="s">
         <v>20</v>
@@ -1328,13 +1379,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
         <v>20</v>
@@ -1342,13 +1393,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B43">
-        <v>18</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
         <v>20</v>
@@ -1356,10 +1407,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44">
-        <v>60</v>
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
       </c>
       <c r="C44" t="s">
         <v>89</v>
@@ -1370,13 +1421,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45">
-        <v>118</v>
+        <v>93</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D45" t="s">
         <v>20</v>
@@ -1384,27 +1435,27 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B46">
-        <v>108</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D46" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47">
-        <v>20</v>
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D47" t="s">
         <v>20</v>
@@ -1412,13 +1463,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48">
-        <v>0.46</v>
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D48" t="s">
         <v>20</v>
@@ -1426,41 +1477,41 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49">
-        <v>0.08</v>
+        <v>100</v>
+      </c>
+      <c r="B49" t="s">
+        <v>101</v>
       </c>
       <c r="C49" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+      <c r="B50">
+        <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D51" t="s">
         <v>20</v>
@@ -1468,13 +1519,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B52">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
         <v>20</v>
@@ -1482,13 +1533,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B53">
-        <v>15.2</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D53" t="s">
         <v>20</v>
@@ -1496,13 +1547,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="B54">
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D54" t="s">
         <v>20</v>
@@ -1510,27 +1561,27 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55">
         <v>108</v>
       </c>
-      <c r="B55">
-        <v>23.5</v>
-      </c>
       <c r="C55" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D55" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B56">
-        <v>15.2</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D56" t="s">
         <v>20</v>
@@ -1538,24 +1589,24 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>110</v>
-      </c>
-      <c r="B57" t="s">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="B57">
+        <v>0.46</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D57" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" t="s">
         <v>114</v>
+      </c>
+      <c r="B58">
+        <v>0.08</v>
       </c>
       <c r="C58" t="s">
         <v>115</v>
@@ -1568,11 +1619,11 @@
       <c r="A59" t="s">
         <v>116</v>
       </c>
-      <c r="B59">
-        <v>1.45</v>
+      <c r="B59" t="s">
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>47</v>
@@ -1580,13 +1631,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>117</v>
-      </c>
-      <c r="B60">
-        <v>6</v>
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D60" t="s">
         <v>20</v>
@@ -1594,13 +1645,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="D61" t="s">
         <v>20</v>
@@ -1608,13 +1659,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="C62" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="D62" t="s">
         <v>20</v>
@@ -1622,13 +1673,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>120</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>124</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>121</v>
       </c>
       <c r="D63" t="s">
         <v>20</v>
@@ -1636,27 +1687,27 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64">
+        <v>23.5</v>
+      </c>
+      <c r="C64" t="s">
         <v>121</v>
       </c>
-      <c r="B64" t="s">
-        <v>122</v>
-      </c>
-      <c r="C64" t="s">
-        <v>123</v>
-      </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B65">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
         <v>20</v>
@@ -1664,27 +1715,27 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66">
-        <v>18</v>
+        <v>128</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
       </c>
       <c r="C66" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="D67" t="s">
         <v>47</v>
@@ -1692,13 +1743,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68" t="s">
-        <v>129</v>
+        <v>134</v>
+      </c>
+      <c r="B68">
+        <v>1.45</v>
       </c>
       <c r="C68" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D68" t="s">
         <v>47</v>
@@ -1706,27 +1757,27 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>131</v>
-      </c>
-      <c r="B69" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="D69" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>133</v>
-      </c>
-      <c r="B70" t="s">
-        <v>111</v>
+        <v>136</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="D70" t="s">
         <v>20</v>
@@ -1734,43 +1785,169 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>135</v>
-      </c>
-      <c r="B71" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="B71">
+        <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="D71" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>138</v>
       </c>
-      <c r="B72" t="s">
-        <v>139</v>
+      <c r="B72">
+        <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" t="s">
         <v>141</v>
       </c>
-      <c r="B73" t="s">
+      <c r="D73" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
         <v>142</v>
       </c>
-      <c r="C73" t="s">
+      <c r="B74">
+        <v>20</v>
+      </c>
+      <c r="C74" t="s">
+        <v>54</v>
+      </c>
+      <c r="D74" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
         <v>143</v>
       </c>
-      <c r="D73" t="s">
+      <c r="B75">
+        <v>18</v>
+      </c>
+      <c r="C75" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>144</v>
+      </c>
+      <c r="B76" t="s">
+        <v>129</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>145</v>
+      </c>
+      <c r="B77" t="s">
+        <v>146</v>
+      </c>
+      <c r="C77" t="s">
+        <v>147</v>
+      </c>
+      <c r="D77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" t="s">
+        <v>46</v>
+      </c>
+      <c r="D78" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" t="s">
+        <v>129</v>
+      </c>
+      <c r="C79" t="s">
+        <v>151</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B80" t="s">
+        <v>153</v>
+      </c>
+      <c r="C80" t="s">
+        <v>154</v>
+      </c>
+      <c r="D80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
+      <c r="B81" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" t="s">
+        <v>157</v>
+      </c>
+      <c r="D81" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" t="s">
+        <v>160</v>
+      </c>
+      <c r="D82" t="s">
         <v>47</v>
       </c>
     </row>
